--- a/refs/heads/main/StructureDefinition-DDCCQuestionnaireResponse.xlsx
+++ b/refs/heads/main/StructureDefinition-DDCCQuestionnaireResponse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T21:40:28+00:00</t>
+    <t>2023-12-14T13:07:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-DDCCQuestionnaireResponse.xlsx
+++ b/refs/heads/main/StructureDefinition-DDCCQuestionnaireResponse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-14T13:07:01+00:00</t>
+    <t>2023-12-14T13:50:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-DDCCQuestionnaireResponse.xlsx
+++ b/refs/heads/main/StructureDefinition-DDCCQuestionnaireResponse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-14T13:50:56+00:00</t>
+    <t>2023-12-15T03:05:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-DDCCQuestionnaireResponse.xlsx
+++ b/refs/heads/main/StructureDefinition-DDCCQuestionnaireResponse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T03:05:37+00:00</t>
+    <t>2024-01-19T16:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-DDCCQuestionnaireResponse.xlsx
+++ b/refs/heads/main/StructureDefinition-DDCCQuestionnaireResponse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-19T16:18:21+00:00</t>
+    <t>2024-04-24T00:11:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-DDCCQuestionnaireResponse.xlsx
+++ b/refs/heads/main/StructureDefinition-DDCCQuestionnaireResponse.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$44</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="346">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T00:11:34+00:00</t>
+    <t>2024-07-30T07:55:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>WHO (http://who.int)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -127,6 +127,123 @@
   </si>
   <si>
     <t>constraint</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Path</t>
+  </si>
+  <si>
+    <t>Slice Name</t>
+  </si>
+  <si>
+    <t>Alias(s)</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Must Support?</t>
+  </si>
+  <si>
+    <t>Is Modifier?</t>
+  </si>
+  <si>
+    <t>Is Summary?</t>
+  </si>
+  <si>
+    <t>Type(s)</t>
+  </si>
+  <si>
+    <t>Short</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Requirements</t>
+  </si>
+  <si>
+    <t>Default Value</t>
+  </si>
+  <si>
+    <t>Meaning When Missing</t>
+  </si>
+  <si>
+    <t>Fixed Value</t>
+  </si>
+  <si>
+    <t>Pattern</t>
+  </si>
+  <si>
+    <t>Example</t>
+  </si>
+  <si>
+    <t>Minimum Value</t>
+  </si>
+  <si>
+    <t>Maximum Value</t>
+  </si>
+  <si>
+    <t>Maximum Length</t>
+  </si>
+  <si>
+    <t>Binding Strength</t>
+  </si>
+  <si>
+    <t>Binding Description</t>
+  </si>
+  <si>
+    <t>Binding Value Set</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Slicing Discriminator</t>
+  </si>
+  <si>
+    <t>Slicing Description</t>
+  </si>
+  <si>
+    <t>Slicing Ordered</t>
+  </si>
+  <si>
+    <t>Slicing Rules</t>
+  </si>
+  <si>
+    <t>Base Path</t>
+  </si>
+  <si>
+    <t>Base Min</t>
+  </si>
+  <si>
+    <t>Base Max</t>
+  </si>
+  <si>
+    <t>Condition(s)</t>
+  </si>
+  <si>
+    <t>Constraint(s)</t>
+  </si>
+  <si>
+    <t>Mapping: Workflow Pattern</t>
+  </si>
+  <si>
+    <t>Mapping: RIM Mapping</t>
+  </si>
+  <si>
+    <t>Mapping: FiveWs Pattern Mapping</t>
   </si>
   <si>
     <t>Form
@@ -156,13 +273,16 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}sdcqr-1:Subject SHOULD be present (searching is difficult without subject).  Almost all QuestionnaireResponses should be with respect to some sort of subject. {subject.exists()}sdcqr-2:When repeats=true for a group, it'll be represented with multiple items with the same linkId in the QuestionnaireResponse.  For a question, it'll be represented by a single item with that linkId with multiple answers. {(QuestionnaireResponse|repeat(answer|item)).select(item.where(answer.value.exists()).linkId.isDistinct()).allTrue()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}sdcqr-1:Subject SHOULD be present (searching is difficult without subject).  Almost all QuestionnaireResponses should be with respect to some sort of subject. {subject.exists()}sdcqr-2:When repeats=true for a group, it'll be represented with multiple items with the same linkId in the QuestionnaireResponse.  For a question, it'll be represented by a single item with that linkId with multiple answers. {(QuestionnaireResponse|repeat(answer|item)).select(item.where(answer.value.exists()).linkId.isDistinct()).allTrue()}</t>
   </si>
   <si>
     <t>Event</t>
   </si>
   <si>
     <t>Observation[moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>infrastructure.information</t>
   </si>
   <si>
     <t>QuestionnaireResponse.id</t>
@@ -248,7 +368,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -306,6 +426,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -352,439 +476,443 @@
     <t>Represents a wet or electronic signature for either the form overall or for the question or item it's associated with.</t>
   </si>
   <si>
+    <t>QuestionnaireResponse.extension:completionMode</t>
+  </si>
+  <si>
+    <t>completionMode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {questionnaireresponse-completionMode}
+</t>
+  </si>
+  <si>
+    <t>E.g. Verbal, written, electronic</t>
+  </si>
+  <si>
+    <t>Indicates how the individual completing the QuestionnaireResponse provided their responses.</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Unique id for this set of answers</t>
+  </si>
+  <si>
+    <t>A business identifier assigned to a particular completed (or partially completed) questionnaire.</t>
+  </si>
+  <si>
+    <t>Used for tracking, registration and other business purposes.</t>
+  </si>
+  <si>
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.basedOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">order
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(CarePlan|ServiceRequest)
+</t>
+  </si>
+  <si>
+    <t>Request fulfilled by this QuestionnaireResponse</t>
+  </si>
+  <si>
+    <t>The order, proposal or plan that is fulfilled in whole or in part by this QuestionnaireResponse.  For example, a ServiceRequest seeking an intake assessment or a decision support recommendation to assess for post-partum depression.</t>
+  </si>
+  <si>
+    <t>Supports traceability of responsibility for the action and allows linkage of an action to the recommendations acted upon.</t>
+  </si>
+  <si>
+    <t>Event.basedOn</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=FLFS].target</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.partOf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Observation|Procedure)
+</t>
+  </si>
+  <si>
+    <t>Part of this action</t>
+  </si>
+  <si>
+    <t>A procedure or observation that this questionnaire was performed as part of the execution of.  For example, the surgery a checklist was executed as part of.</t>
+  </si>
+  <si>
+    <t>Composition of questionnaire responses will be handled by the parent questionnaire having answers that reference the child questionnaire.  For relationships to referrals, and other types of requests, use basedOn.</t>
+  </si>
+  <si>
+    <t>Event.partOf</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=COMP].source[moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.questionnaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Form
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire)
+</t>
+  </si>
+  <si>
+    <t>Form being answered</t>
+  </si>
+  <si>
+    <t>The Questionnaire that defines and organizes the questions for which answers are being provided.</t>
+  </si>
+  <si>
+    <t>For SDC, this SHALL be the version-specific URL of the form as hosted on the Form Manager.</t>
+  </si>
+  <si>
+    <t>Needed to allow editing of the questionnaire response in a manner that enforces the constraints of the original form.</t>
+  </si>
+  <si>
+    <t>Event.instantiates</t>
+  </si>
+  <si>
+    <t>./outboundRelationship[typeCode=INST]/target[classCode=OBS, moodCode=DEFN]</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.questionnaire.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>xml:id (or equivalent in JSON)</t>
+  </si>
+  <si>
+    <t>unique id for the element within a resource (for internal references)</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.questionnaire.extension</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.questionnaire.extension:questionnaireDisplay</t>
+  </si>
+  <si>
+    <t>questionnaireDisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {display}
+</t>
+  </si>
+  <si>
+    <t>Display name for canonical reference</t>
+  </si>
+  <si>
+    <t>The title or other name to display when referencing a resource by canonical URL.</t>
+  </si>
+  <si>
+    <t>This SHALL be the title of the Questionnaire at the time the QuestionnaireResponse was originally authored.</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.questionnaire.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical
+</t>
+  </si>
+  <si>
+    <t>Primitive value for canonical</t>
+  </si>
+  <si>
+    <t>uri.value</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.status</t>
+  </si>
+  <si>
+    <t>in-progress | completed | amended | entered-in-error | stopped</t>
+  </si>
+  <si>
+    <t>The position of the questionnaire response within its overall lifecycle.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
+  </si>
+  <si>
+    <t>The information on Questionnaire resources  may possibly be gathered during multiple sessions and altered after considered being finished.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Lifecycle status of the questionnaire response.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/questionnaire-answers-status|4.3.0</t>
+  </si>
+  <si>
+    <t>Event.status</t>
+  </si>
+  <si>
+    <t>.statusCode (also whether there's a revisionControlAct - and possibly mood to distinguish "in-progress" from "published)</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.subject</t>
+  </si>
+  <si>
+    <t>Patient
+Focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Resource)
+</t>
+  </si>
+  <si>
+    <t>The subject of the questions</t>
+  </si>
+  <si>
+    <t>The subject of the questionnaire response.  This could be a patient, organization, practitioner, device, etc.  This is who/what the answers apply to, but is not necessarily the source of information.</t>
+  </si>
+  <si>
+    <t>If the Questionnaire declared a subjectType, the resource pointed to by this element must be an instance of one of the listed types.
+  If subject is omitted - because the QuestionnaireResponse is not associated with a specific subject, ensure that QuestionnaireRsponse.identifier is present or the QuestionnaireResponse is referenced somewhere (e.g. Task.output, Composition.section.entry, etc.) to allow tracking and retrieval of the QuestionnaireResponse</t>
+  </si>
+  <si>
+    <t>Allows linking the answers to the individual the answers describe.  May also affect access control.</t>
+  </si>
+  <si>
+    <t>Event.subject</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=SBJ].role</t>
+  </si>
+  <si>
+    <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.encounter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Encounter)
+</t>
+  </si>
+  <si>
+    <t>Encounter created as part of</t>
+  </si>
+  <si>
+    <t>The Encounter during which this questionnaire response was created or to which the creation of this record is tightly associated.</t>
+  </si>
+  <si>
+    <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter. A questionnaire that was initiated during an encounter but not fully completed during the encounter would still generally be associated with the encounter.</t>
+  </si>
+  <si>
+    <t>Provides context for the information that was captured.  May also affect access control.</t>
+  </si>
+  <si>
+    <t>Event.encounter</t>
+  </si>
+  <si>
+    <t>.inboundRelationship(typeCode=COMP].source[classCode&lt;=PCPR, moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>FiveWs.context</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.authored</t>
+  </si>
+  <si>
+    <t>Date Created
+Date publishedDate IssuedDate updated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Date the answers were gathered</t>
+  </si>
+  <si>
+    <t>Identifies when this version of the answer set was created.  Changes whenever the answers are updated.</t>
+  </si>
+  <si>
+    <t>May be different from the lastUpdateTime of the resource itself, because that reflects when the data was known to the server, not when the data was captured.
+This element is optional to allow for systems that might not know the value, however it SHOULD be populated if possible.</t>
+  </si>
+  <si>
+    <t>Clinicians need to be able to check the date that the information in the questionnaire was collected, to derive the context of the answers.</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=AUT].time</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.author</t>
+  </si>
+  <si>
+    <t>Laboratory
+ServicePractitionerDepartmentCompanyPerformer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Device|Practitioner|PractitionerRole|Patient|RelatedPerson|Organization)
+</t>
+  </si>
+  <si>
+    <t>Person who received and recorded the answers</t>
+  </si>
+  <si>
+    <t>Person who received the answers to the questions in the QuestionnaireResponse and recorded them in the system.</t>
+  </si>
+  <si>
+    <t>Mapping a subject's answers to multiple choice options and determining what to put in the textual answer is a matter of interpretation.  Authoring by device would indicate that some portion of the questionnaire had been auto-populated.</t>
+  </si>
+  <si>
+    <t>Need to know who interpreted the subject's answers to the questions in the questionnaire, and selected the appropriate options for answers.</t>
+  </si>
+  <si>
+    <t>Event.performer</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=AUT].role</t>
+  </si>
+  <si>
+    <t>FiveWs.author</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson)
+</t>
+  </si>
+  <si>
+    <t>The person who answered the questions</t>
+  </si>
+  <si>
+    <t>The person who answered the questions about the subject.</t>
+  </si>
+  <si>
+    <t>If not specified, no inference can be made about who provided the data.</t>
+  </si>
+  <si>
+    <t>When answering questions about a subject that is minor, incapable of answering or an animal, another human source may answer the questions.</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=INF].role</t>
+  </si>
+  <si>
+    <t>FiveWs.source</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Groups and questions</t>
+  </si>
+  <si>
+    <t>A group or question item from the original questionnaire for which answers are provided.</t>
+  </si>
+  <si>
+    <t>Groups cannot have answers and therefore must nest directly within item. When dealing with questions, nesting must occur within each answer because some questions may have multiple answers (and the nesting occurs for each answer).</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+qrs-1:Nested item can't be beneath both item and answer {(answer.exists() and item.exists()).not()}</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COMP].target[classCode=OBS, moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.extension</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.extension:itemMedia</t>
+  </si>
+  <si>
+    <t>itemMedia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-itemMedia}
+</t>
+  </si>
+  <si>
+    <t>Media to display</t>
+  </si>
+  <si>
+    <t>Media to render/make available as an accompaniment to the question being asked</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t>QuestionnaireResponse.extension:completionMode</t>
-  </si>
-  <si>
-    <t>completionMode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {questionnaireresponse-completionMode}
-</t>
-  </si>
-  <si>
-    <t>E.g. Verbal, written, electronic</t>
-  </si>
-  <si>
-    <t>Indicates how the individual completing the QuestionnaireResponse provided their responses.</t>
-  </si>
-  <si>
-    <t>QuestionnaireResponse.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>QuestionnaireResponse.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Unique id for this set of answers</t>
-  </si>
-  <si>
-    <t>A business identifier assigned to a particular completed (or partially completed) questionnaire.</t>
-  </si>
-  <si>
-    <t>Used for tracking, registration and other business purposes.</t>
-  </si>
-  <si>
-    <t>Event.identifier</t>
-  </si>
-  <si>
-    <t>.id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>QuestionnaireResponse.basedOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">order
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(CarePlan|ServiceRequest)
-</t>
-  </si>
-  <si>
-    <t>Request fulfilled by this QuestionnaireResponse</t>
-  </si>
-  <si>
-    <t>The order, proposal or plan that is fulfilled in whole or in part by this QuestionnaireResponse.  For example, a ServiceRequest seeking an intake assessment or a decision support recommendation to assess for post-partum depression.</t>
-  </si>
-  <si>
-    <t>Supports traceability of responsibility for the action and allows linkage of an action to the recommendations acted upon.</t>
-  </si>
-  <si>
-    <t>Event.basedOn</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=FLFS].target</t>
-  </si>
-  <si>
-    <t>QuestionnaireResponse.partOf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Observation|Procedure)
-</t>
-  </si>
-  <si>
-    <t>Part of this action</t>
-  </si>
-  <si>
-    <t>A procedure or observation that this questionnaire was performed as part of the execution of.  For example, the surgery a checklist was executed as part of.</t>
-  </si>
-  <si>
-    <t>Composition of questionnaire responses will be handled by the parent questionnaire having answers that reference the child questionnaire.  For relationships to referrals, and other types of requests, use basedOn.</t>
-  </si>
-  <si>
-    <t>Event.partOf</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=COMP].source[moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>QuestionnaireResponse.questionnaire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Form
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire)
-</t>
-  </si>
-  <si>
-    <t>Form being answered</t>
-  </si>
-  <si>
-    <t>The Questionnaire that defines and organizes the questions for which answers are being provided.</t>
-  </si>
-  <si>
-    <t>For SDC, this SHALL be the version-specific URL of the form as hosted on the Form Manager.</t>
-  </si>
-  <si>
-    <t>Needed to allow editing of the questionnaire response in a manner that enforces the constraints of the original form.</t>
-  </si>
-  <si>
-    <t>Event.instantiates</t>
-  </si>
-  <si>
-    <t>./outboundRelationship[typeCode=INST]/target[classCode=OBS, moodCode=DEFN]</t>
-  </si>
-  <si>
-    <t>QuestionnaireResponse.questionnaire.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>xml:id (or equivalent in JSON)</t>
-  </si>
-  <si>
-    <t>unique id for the element within a resource (for internal references)</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>QuestionnaireResponse.questionnaire.extension</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>QuestionnaireResponse.questionnaire.extension:questionnaireDisplay</t>
-  </si>
-  <si>
-    <t>questionnaireDisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {display}
-</t>
-  </si>
-  <si>
-    <t>Display name for canonical reference</t>
-  </si>
-  <si>
-    <t>The title or other name to display when referencing a resource by canonical URL.</t>
-  </si>
-  <si>
-    <t>This SHALL be the title of the Questionnaire at the time the QuestionnaireResponse was originally authored.</t>
-  </si>
-  <si>
-    <t>QuestionnaireResponse.questionnaire.value</t>
-  </si>
-  <si>
-    <t>Primitive value for canonical</t>
-  </si>
-  <si>
-    <t>uri.value</t>
-  </si>
-  <si>
-    <t>QuestionnaireResponse.status</t>
-  </si>
-  <si>
-    <t>in-progress | completed | amended | entered-in-error | stopped</t>
-  </si>
-  <si>
-    <t>The position of the questionnaire response within its overall lifecycle.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
-  </si>
-  <si>
-    <t>The information on Questionnaire resources  may possibly be gathered during multiple sessions and altered after considered being finished.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Lifecycle status of the questionnaire response.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/questionnaire-answers-status|4.0.1</t>
-  </si>
-  <si>
-    <t>Event.status</t>
-  </si>
-  <si>
-    <t>.statusCode (also whether there's a revisionControlAct - and possibly mood to distinguish "in-progress" from "published)</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>QuestionnaireResponse.subject</t>
-  </si>
-  <si>
-    <t>Patient
-Focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Resource)
-</t>
-  </si>
-  <si>
-    <t>The subject of the questions</t>
-  </si>
-  <si>
-    <t>The subject of the questionnaire response.  This could be a patient, organization, practitioner, device, etc.  This is who/what the answers apply to, but is not necessarily the source of information.</t>
-  </si>
-  <si>
-    <t>If the Questionnaire declared a subjectType, the resource pointed to by this element must be an instance of one of the listed types.
-  If subject is omitted - because the QuestionnaireResponse is not associated with a specific subject, ensure that QuestionnaireRsponse.identifier is present or the QuestionnaireResponse is referenced somewhere (e.g. Task.output, Composition.section.entry, etc.) to allow tracking and retrieval of the QuestionnaireResponse</t>
-  </si>
-  <si>
-    <t>Allows linking the answers to the individual the answers describe.  May also affect access control.</t>
-  </si>
-  <si>
-    <t>Event.subject</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=SBJ].role</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>QuestionnaireResponse.encounter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Encounter)
-</t>
-  </si>
-  <si>
-    <t>Encounter created as part of</t>
-  </si>
-  <si>
-    <t>The Encounter during which this questionnaire response was created or to which the creation of this record is tightly associated.</t>
-  </si>
-  <si>
-    <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter. A questionnaire that was initiated during an encounter but not fully completed during the encounter would still generally be associated with the encounter.</t>
-  </si>
-  <si>
-    <t>Provides context for the information that was captured.  May also affect access control.</t>
-  </si>
-  <si>
-    <t>Event.encounter</t>
-  </si>
-  <si>
-    <t>.inboundRelationship(typeCode=COMP].source[classCode&lt;=PCPR, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>FiveWs.context</t>
-  </si>
-  <si>
-    <t>QuestionnaireResponse.authored</t>
-  </si>
-  <si>
-    <t>Date Created
-Date publishedDate IssuedDate updated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Date the answers were gathered</t>
-  </si>
-  <si>
-    <t>Identifies when this version of the answer set was created.  Changes whenever the answers are updated.</t>
-  </si>
-  <si>
-    <t>May be different from the lastUpdateTime of the resource itself, because that reflects when the data was known to the server, not when the data was captured.
-This element is optional to allow for systems that might not know the value, however it SHOULD be populated if possible.</t>
-  </si>
-  <si>
-    <t>Clinicians need to be able to check the date that the information in the questionnaire was collected, to derive the context of the answers.</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>QuestionnaireResponse.author</t>
-  </si>
-  <si>
-    <t>Laboratory
-ServicePractitionerDepartmentCompanyPerformer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Device|Practitioner|PractitionerRole|Patient|RelatedPerson|Organization)
-</t>
-  </si>
-  <si>
-    <t>Person who received and recorded the answers</t>
-  </si>
-  <si>
-    <t>Person who received the answers to the questions in the QuestionnaireResponse and recorded them in the system.</t>
-  </si>
-  <si>
-    <t>Mapping a subject's answers to multiple choice options and determining what to put in the textual answer is a matter of interpretation.  Authoring by device would indicate that some portion of the questionnaire had been auto-populated.</t>
-  </si>
-  <si>
-    <t>Need to know who interpreted the subject's answers to the questions in the questionnaire, and selected the appropriate options for answers.</t>
-  </si>
-  <si>
-    <t>Event.performer</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=AUT].role</t>
-  </si>
-  <si>
-    <t>FiveWs.author</t>
-  </si>
-  <si>
-    <t>QuestionnaireResponse.source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson)
-</t>
-  </si>
-  <si>
-    <t>The person who answered the questions</t>
-  </si>
-  <si>
-    <t>The person who answered the questions about the subject.</t>
-  </si>
-  <si>
-    <t>If not specified, no inference can be made about who provided the data.</t>
-  </si>
-  <si>
-    <t>When answering questions about a subject that is minor, incapable of answering or an animal, another human source may answer the questions.</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=INF].role</t>
-  </si>
-  <si>
-    <t>FiveWs.source</t>
-  </si>
-  <si>
-    <t>QuestionnaireResponse.item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Groups and questions</t>
-  </si>
-  <si>
-    <t>A group or question item from the original questionnaire for which answers are provided.</t>
-  </si>
-  <si>
-    <t>Groups cannot have answers and therefore must nest directly within item. When dealing with questions, nesting must occur within each answer because some questions may have multiple answers (and the nesting occurs for each answer).</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qrs-1:Nested item can't be beneath both item and answer {(answer.exists() and item.exists()).not()}</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=COMP].target[classCode=OBS, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>QuestionnaireResponse.item.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>QuestionnaireResponse.item.extension</t>
-  </si>
-  <si>
-    <t>QuestionnaireResponse.item.extension:itemMedia</t>
-  </si>
-  <si>
-    <t>itemMedia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-itemMedia}
-</t>
-  </si>
-  <si>
-    <t>Media to display</t>
-  </si>
-  <si>
-    <t>Media to render/make available as an accompaniment to the question being asked</t>
-  </si>
-  <si>
     <t>QuestionnaireResponse.item.extension:ItemSignature</t>
   </si>
   <si>
@@ -829,10 +957,10 @@
     <t>ElementDefinition - details for the item</t>
   </si>
   <si>
-    <t>A reference to an [ElementDefinition](http://hl7.org/fhir/R4/elementdefinition.html) that provides the details for the item.</t>
-  </si>
-  <si>
-    <t>The ElementDefinition must be in a [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#), and must have a fragment identifier that identifies the specific data element by its id (Element.id). E.g. http://hl7.org/fhir/StructureDefinition/Observation#Observation.value[x].
+    <t>A reference to an [ElementDefinition](http://hl7.org/fhir/R4B/elementdefinition.html) that provides the details for the item.</t>
+  </si>
+  <si>
+    <t>The ElementDefinition must be in a [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#), and must have a fragment identifier that identifies the specific data element by its id (Element.id). E.g. http://hl7.org/fhir/StructureDefinition/Observation#Observation.value[x].
 There is no need for this element if the item pointed to by the linkId has a definition listed.</t>
   </si>
   <si>
@@ -867,6 +995,10 @@
   </si>
   <si>
     <t>The value is nested because we cannot have a repeating structure that has variable type.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
   </si>
   <si>
     <t>.value[type=LIST_ANY]</t>
@@ -911,8 +1043,12 @@
 manipulation of a concept (e.g. Adding up components of a score). Scores are usually a whole number, but occasionally decimals are encountered in scores.</t>
   </si>
   <si>
-    <t>Scores are commonly encountered in various clinical assessment scales. Assigning a value to a concept should generally be done in a formal code system that defines the value, or in an applicable value set for the concept, but some concepts do not have a formal definition (or are not even represented as a concept formally, especially in [Questionnaires](http://hl7.org/fhir/R4/questionnaire.html), 
+    <t>Scores are commonly encountered in various clinical assessment scales. Assigning a value to a concept should generally be done in a formal code system that defines the value, or in an applicable value set for the concept, but some concepts do not have a formal definition (or are not even represented as a concept formally, especially in [Questionnaires](http://hl7.org/fhir/R4B/questionnaire.html), 
 so this extension is allowed to appear ouside those preferred contexts.  Scores may even be assigned arbitrarily during use (hence, on Coding). The value may be constrained to an integer in some contexts of use. Todo: Scoring algorithms may also be defined directly, but how this is done is not yet defined.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>QuestionnaireResponse.item.answer.modifierExtension</t>
@@ -940,7 +1076,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>Code indicating the response provided for a question.</t>
+    <t>Binding this is problematic because one value set can't apply to both codes and quantities.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/questionnaire-answers</t>
@@ -1287,17 +1423,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM43"/>
+  <dimension ref="A1:AM44"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="65.51171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="51.9375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="20.3984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="47.421875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="6" max="6" width="2.2109375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="2.2109375" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="2.1640625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="2.1640625" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="87.4609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1305,4807 +1442,4926 @@
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="9.6640625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="50.4609375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.94140625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="58.64453125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="10.26171875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="5.62109375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="42.84375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="2.2109375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="2.2109375" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="20.703125" customWidth="true"/>
+    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="19.62890625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="111.80859375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="16.3984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B1" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="C1" s="2"/>
-      <c r="D1" t="s" s="2">
+      <c r="A1" t="s" s="1">
         <v>37</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" t="s" s="2">
+      <c r="B1" t="s" s="1">
         <v>38</v>
       </c>
-      <c r="G1" t="s" s="2">
+      <c r="C1" t="s" s="1">
         <v>39</v>
       </c>
-      <c r="H1" t="s" s="2">
+      <c r="D1" t="s" s="1">
         <v>40</v>
       </c>
-      <c r="I1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="J1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="K1" t="s" s="2">
+      <c r="E1" t="s" s="1">
         <v>41</v>
       </c>
-      <c r="L1" t="s" s="2">
+      <c r="F1" t="s" s="1">
         <v>42</v>
       </c>
-      <c r="M1" t="s" s="2">
+      <c r="G1" t="s" s="1">
         <v>43</v>
       </c>
-      <c r="N1" t="s" s="2">
+      <c r="H1" t="s" s="1">
         <v>44</v>
       </c>
-      <c r="O1" s="2"/>
-      <c r="P1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="Q1" s="2"/>
-      <c r="R1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="S1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="T1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="U1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="V1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="W1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="X1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="Y1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="Z1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AA1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AB1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AC1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AD1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AE1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AF1" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="AG1" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AH1" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="AI1" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AJ1" t="s" s="2">
+      <c r="I1" t="s" s="1">
         <v>45</v>
       </c>
-      <c r="AK1" t="s" s="2">
+      <c r="J1" t="s" s="1">
         <v>46</v>
       </c>
-      <c r="AL1" t="s" s="2">
+      <c r="K1" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="AM1" t="s" s="2">
-        <v>40</v>
+      <c r="L1" t="s" s="1">
+        <v>48</v>
+      </c>
+      <c r="M1" t="s" s="1">
+        <v>49</v>
+      </c>
+      <c r="N1" t="s" s="1">
+        <v>50</v>
+      </c>
+      <c r="O1" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="P1" t="s" s="1">
+        <v>52</v>
+      </c>
+      <c r="Q1" t="s" s="1">
+        <v>53</v>
+      </c>
+      <c r="R1" t="s" s="1">
+        <v>54</v>
+      </c>
+      <c r="S1" t="s" s="1">
+        <v>55</v>
+      </c>
+      <c r="T1" t="s" s="1">
+        <v>56</v>
+      </c>
+      <c r="U1" t="s" s="1">
+        <v>57</v>
+      </c>
+      <c r="V1" t="s" s="1">
+        <v>58</v>
+      </c>
+      <c r="W1" t="s" s="1">
+        <v>59</v>
+      </c>
+      <c r="X1" t="s" s="1">
+        <v>60</v>
+      </c>
+      <c r="Y1" t="s" s="1">
+        <v>61</v>
+      </c>
+      <c r="Z1" t="s" s="1">
+        <v>62</v>
+      </c>
+      <c r="AA1" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="AB1" t="s" s="1">
+        <v>64</v>
+      </c>
+      <c r="AC1" t="s" s="1">
+        <v>65</v>
+      </c>
+      <c r="AD1" t="s" s="1">
+        <v>66</v>
+      </c>
+      <c r="AE1" t="s" s="1">
+        <v>67</v>
+      </c>
+      <c r="AF1" t="s" s="1">
+        <v>68</v>
+      </c>
+      <c r="AG1" t="s" s="1">
+        <v>69</v>
+      </c>
+      <c r="AH1" t="s" s="1">
+        <v>70</v>
+      </c>
+      <c r="AI1" t="s" s="1">
+        <v>71</v>
+      </c>
+      <c r="AJ1" t="s" s="1">
+        <v>72</v>
+      </c>
+      <c r="AK1" t="s" s="1">
+        <v>73</v>
+      </c>
+      <c r="AL1" t="s" s="1">
+        <v>74</v>
+      </c>
+      <c r="AM1" t="s" s="1">
+        <v>75</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>40</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="N3" s="2"/>
+        <v>93</v>
+      </c>
+      <c r="N3" t="s" s="2">
+        <v>94</v>
+      </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AM3" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="N4" t="s" s="2">
-        <v>66</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>40</v>
+        <v>113</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>40</v>
+        <v>114</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>40</v>
+        <v>115</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="N8" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="N8" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S8" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U8" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V8" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W8" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA8" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AC8" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD8" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>40</v>
+        <v>133</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>102</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S9" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U9" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V9" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W9" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>40</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>40</v>
+        <v>139</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>111</v>
+        <v>146</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T10" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U10" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V10" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W10" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA10" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD10" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="D11" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>94</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U11" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V11" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W11" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA11" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD11" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>119</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>119</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>40</v>
+        <v>153</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="O12" t="s" s="2">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="P12" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T12" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U12" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V12" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W12" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA12" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD12" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>119</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>126</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="P13" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T13" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U13" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V13" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W13" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA13" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD13" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>40</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>40</v>
+        <v>168</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>137</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O14" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="P14" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA14" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD14" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>143</v>
+        <v>79</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U15" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V15" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD15" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>40</v>
+        <v>183</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>153</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="P16" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U16" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V16" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W16" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA16" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD16" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>40</v>
+        <v>189</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>40</v>
+        <v>190</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>94</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>95</v>
+        <v>193</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>96</v>
+        <v>194</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V17" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AC17" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD17" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>40</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC18" s="2"/>
       <c r="AD18" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>40</v>
+        <v>139</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="D19" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>152</v>
+        <v>200</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>165</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U19" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V19" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W19" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA19" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD19" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>167</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>167</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>69</v>
+        <v>205</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>168</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>172</v>
+        <v>79</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>167</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>175</v>
+        <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>176</v>
+        <v>79</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>177</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>180</v>
+        <v>109</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>183</v>
+        <v>211</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>184</v>
+        <v>212</v>
       </c>
       <c r="P21" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>40</v>
+        <v>213</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>40</v>
+        <v>214</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>40</v>
+        <v>215</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>187</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>40</v>
+        <v>220</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="P22" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>196</v>
+        <v>228</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>198</v>
+        <v>79</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>199</v>
+        <v>230</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="P23" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U23" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V23" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA23" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD23" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>206</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>208</v>
+        <v>239</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="P24" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>216</v>
+        <v>247</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>217</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>217</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>40</v>
+        <v>249</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>219</v>
+        <v>251</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>222</v>
+        <v>254</v>
       </c>
       <c r="P25" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD25" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>217</v>
+        <v>248</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>40</v>
+        <v>255</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>223</v>
+        <v>256</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>224</v>
+        <v>257</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>226</v>
+        <v>259</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>227</v>
+        <v>260</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>228</v>
+        <v>261</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="P26" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U26" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V26" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD26" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>230</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>231</v>
+        <v>264</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>40</v>
+        <v>265</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>232</v>
+        <v>266</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>232</v>
+        <v>266</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>152</v>
+        <v>267</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U27" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V27" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>155</v>
+        <v>266</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>40</v>
+        <v>271</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>235</v>
+        <v>272</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>236</v>
+        <v>273</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>236</v>
+        <v>273</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>94</v>
+        <v>192</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>95</v>
+        <v>274</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>96</v>
+        <v>275</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U28" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V28" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AC28" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD28" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>40</v>
+        <v>276</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>237</v>
+        <v>277</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>240</v>
+        <v>136</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>241</v>
+        <v>137</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U29" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V29" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>40</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>40</v>
+        <v>139</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>242</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>236</v>
+        <v>277</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>243</v>
+        <v>279</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>103</v>
+        <v>280</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>104</v>
+        <v>281</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>105</v>
+        <v>282</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>106</v>
+        <v>283</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>244</v>
+        <v>284</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="D31" t="s" s="2">
-        <v>245</v>
+        <v>79</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>246</v>
+        <v>145</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>248</v>
+        <v>197</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>249</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>249</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>40</v>
+        <v>287</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>250</v>
+        <v>288</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="O32" t="s" s="2">
-        <v>252</v>
+        <v>157</v>
       </c>
       <c r="P32" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U32" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V32" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>253</v>
+        <v>133</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>254</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>254</v>
+        <v>291</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>63</v>
+        <v>192</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>258</v>
+        <v>294</v>
       </c>
       <c r="P33" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>254</v>
+        <v>291</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>260</v>
+        <v>296</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>260</v>
+        <v>296</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>152</v>
+        <v>103</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>261</v>
+        <v>297</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="O34" t="s" s="2">
-        <v>263</v>
+        <v>300</v>
       </c>
       <c r="P34" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U34" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V34" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>260</v>
+        <v>296</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>264</v>
+        <v>301</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>265</v>
+        <v>302</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>265</v>
+        <v>302</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>226</v>
+        <v>192</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>266</v>
+        <v>303</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P35" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U35" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V35" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>265</v>
+        <v>302</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>269</v>
+        <v>306</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>152</v>
+        <v>267</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>233</v>
+        <v>308</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U36" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V36" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD36" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>155</v>
+        <v>307</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>40</v>
+        <v>311</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>235</v>
+        <v>312</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>271</v>
+        <v>313</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>271</v>
+        <v>313</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>94</v>
+        <v>192</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>95</v>
+        <v>274</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>96</v>
+        <v>275</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U37" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V37" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA37" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AC37" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD37" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>40</v>
+        <v>276</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>272</v>
+        <v>314</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>274</v>
+        <v>135</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>275</v>
+        <v>136</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>276</v>
+        <v>137</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U38" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V38" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA38" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>40</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC38" s="2"/>
       <c r="AD38" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>40</v>
+        <v>139</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>277</v>
+        <v>315</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>271</v>
+        <v>314</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>278</v>
+        <v>316</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>279</v>
+        <v>317</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>280</v>
+        <v>318</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U39" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V39" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W39" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA39" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD39" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>106</v>
+        <v>283</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>283</v>
+        <v>320</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="C40" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="D40" t="s" s="2">
-        <v>245</v>
+        <v>79</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>94</v>
+        <v>322</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>246</v>
+        <v>323</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>247</v>
+        <v>324</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U40" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V40" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W40" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA40" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD40" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>248</v>
+        <v>197</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>40</v>
+        <v>283</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>326</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>284</v>
+        <v>327</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>284</v>
+        <v>327</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>40</v>
+        <v>287</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>285</v>
+        <v>135</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>288</v>
+        <v>156</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>289</v>
+        <v>157</v>
       </c>
       <c r="P41" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U41" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V41" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W41" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y41" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>284</v>
-      </c>
       <c r="AG41" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>293</v>
+        <v>133</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>294</v>
+        <v>328</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>294</v>
+        <v>328</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>41</v>
+        <v>329</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>295</v>
+        <v>330</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>331</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="O42" t="s" s="2">
-        <v>297</v>
+        <v>333</v>
       </c>
       <c r="P42" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U42" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V42" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W42" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>40</v>
+        <v>334</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>40</v>
+        <v>335</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>40</v>
+        <v>336</v>
       </c>
       <c r="AA42" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD42" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>294</v>
+        <v>328</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>231</v>
+        <v>337</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>298</v>
+        <v>338</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>298</v>
+        <v>338</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>299</v>
+        <v>339</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>301</v>
+        <v>341</v>
       </c>
       <c r="P43" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="U43" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="V43" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="W43" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AA43" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AD43" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>298</v>
+        <v>338</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>40</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="P44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM43">
+  <autoFilter ref="A1:AM44">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6115,7 +6371,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI42">
+  <conditionalFormatting sqref="A2:AI43">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/refs/heads/main/StructureDefinition-DDCCQuestionnaireResponse.xlsx
+++ b/refs/heads/main/StructureDefinition-DDCCQuestionnaireResponse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-30T07:55:09+00:00</t>
+    <t>2024-07-30T11:13:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
